--- a/exports/trend_1d/PAYTM_full_report.xlsx
+++ b/exports/trend_1d/PAYTM_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q31"/>
+  <dimension ref="A1:U31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>31.99</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44568</v>
+        <v>44571</v>
       </c>
       <c r="H2" t="n">
-        <v>1231.6</v>
+        <v>1158.05</v>
       </c>
       <c r="I2" t="n">
         <v>1189.339512547</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K2" t="n">
-        <v>-25.28</v>
+        <v>-29.74</v>
       </c>
       <c r="L2" t="n">
-        <v>25.38</v>
+        <v>30.11</v>
       </c>
       <c r="M2" t="n">
         <v>5</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>16.7</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44659</v>
+        <v>44662</v>
       </c>
       <c r="H3" t="n">
-        <v>616.95</v>
+        <v>687.65</v>
       </c>
       <c r="I3" t="n">
         <v>660.5392703341918</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="K3" t="n">
-        <v>46.73</v>
+        <v>40.62</v>
       </c>
       <c r="L3" t="n">
         <v>6.21</v>
@@ -612,7 +647,7 @@
         <v>3</v>
       </c>
       <c r="N3" t="n">
-        <v>9.550000000000001</v>
+        <v>11.46</v>
       </c>
       <c r="O3" t="n">
         <v>-5.97</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>4</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -648,25 +695,25 @@
         <v>23.79</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44686</v>
+        <v>44687</v>
       </c>
       <c r="H4" t="n">
-        <v>575.2</v>
+        <v>568</v>
       </c>
       <c r="I4" t="n">
         <v>571.4988992129992</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K4" t="n">
-        <v>-16.35</v>
+        <v>-17.4</v>
       </c>
       <c r="L4" t="n">
-        <v>16.82</v>
+        <v>20.5</v>
       </c>
       <c r="M4" t="n">
-        <v>1.23</v>
+        <v>2.47</v>
       </c>
       <c r="N4" t="n">
         <v>4.32</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>15.35</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44701</v>
+        <v>44704</v>
       </c>
       <c r="H5" t="n">
-        <v>575.5</v>
+        <v>619.35</v>
       </c>
       <c r="I5" t="n">
         <v>608.591938437238</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.32</v>
+        <v>-9.039999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>6.74</v>
+        <v>11.18</v>
       </c>
       <c r="M5" t="n">
         <v>2.18</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>22.37</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44802</v>
+        <v>44803</v>
       </c>
       <c r="H6" t="n">
-        <v>726.4</v>
+        <v>717.85</v>
       </c>
       <c r="I6" t="n">
         <v>725.3331244281846</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K6" t="n">
-        <v>17.28</v>
+        <v>15.9</v>
       </c>
       <c r="L6" t="n">
         <v>10.87</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>5</v>
+      </c>
+      <c r="U6" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>12.28</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44841</v>
+        <v>44844</v>
       </c>
       <c r="H7" t="n">
-        <v>707.45</v>
+        <v>727.25</v>
       </c>
       <c r="I7" t="n">
         <v>710.7409791970655</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K7" t="n">
-        <v>1.45</v>
+        <v>-1.31</v>
       </c>
       <c r="L7" t="n">
         <v>4.2</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>10.66</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44853</v>
+        <v>44854</v>
       </c>
       <c r="H8" t="n">
-        <v>652.45</v>
+        <v>632.75</v>
       </c>
       <c r="I8" t="n">
         <v>649.6932759439248</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K8" t="n">
-        <v>-10.29</v>
+        <v>-12.99</v>
       </c>
       <c r="L8" t="n">
-        <v>10.48</v>
+        <v>13.23</v>
       </c>
       <c r="M8" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>2.63</v>
+        <v>3.02</v>
       </c>
       <c r="O8" t="n">
         <v>2.8</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,25 +1040,25 @@
         <v>11.61</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44903</v>
+        <v>44904</v>
       </c>
       <c r="H9" t="n">
-        <v>508.2</v>
+        <v>544.6</v>
       </c>
       <c r="I9" t="n">
         <v>543.1185880666842</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K9" t="n">
-        <v>19.68</v>
+        <v>13.93</v>
       </c>
       <c r="L9" t="n">
         <v>5.63</v>
       </c>
       <c r="M9" t="n">
-        <v>3.14</v>
+        <v>7.04</v>
       </c>
       <c r="N9" t="n">
         <v>7.16</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>15.96</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44951</v>
+        <v>44953</v>
       </c>
       <c r="H10" t="n">
-        <v>532.95</v>
+        <v>513.4</v>
       </c>
       <c r="I10" t="n">
         <v>522.8198964063984</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.14</v>
+        <v>-5.73</v>
       </c>
       <c r="L10" t="n">
         <v>13.33</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>14.92</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44964</v>
+        <v>44965</v>
       </c>
       <c r="H11" t="n">
-        <v>588.6</v>
+        <v>675.95</v>
       </c>
       <c r="I11" t="n">
         <v>589.9827948110034</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K11" t="n">
-        <v>-14.65</v>
+        <v>-31.66</v>
       </c>
       <c r="L11" t="n">
-        <v>30.49</v>
+        <v>35.96</v>
       </c>
       <c r="M11" t="n">
         <v>5.91</v>
       </c>
       <c r="N11" t="n">
-        <v>6.35</v>
+        <v>14.84</v>
       </c>
       <c r="O11" t="n">
         <v>-3.67</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>21.06</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>45002</v>
+        <v>45005</v>
       </c>
       <c r="H12" t="n">
-        <v>578.35</v>
+        <v>559.2</v>
       </c>
       <c r="I12" t="n">
         <v>570.7929736804094</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K12" t="n">
-        <v>-14.44</v>
+        <v>-17.27</v>
       </c>
       <c r="L12" t="n">
-        <v>16.7</v>
+        <v>17.74</v>
       </c>
       <c r="M12" t="n">
         <v>0.73</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>13.95</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>45016</v>
+        <v>45019</v>
       </c>
       <c r="H13" t="n">
-        <v>636.8</v>
+        <v>639</v>
       </c>
       <c r="I13" t="n">
         <v>637.2021615212225</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K13" t="n">
-        <v>-13.88</v>
+        <v>-14.27</v>
       </c>
       <c r="L13" t="n">
         <v>17.29</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>11.53</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>45128</v>
+        <v>45131</v>
       </c>
       <c r="H14" t="n">
-        <v>844.3</v>
+        <v>802</v>
       </c>
       <c r="I14" t="n">
         <v>806.2003298103359</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="K14" t="n">
-        <v>32.13</v>
+        <v>25.51</v>
       </c>
       <c r="L14" t="n">
         <v>1.25</v>
       </c>
       <c r="M14" t="n">
-        <v>0.28</v>
+        <v>0.51</v>
       </c>
       <c r="N14" t="n">
-        <v>3.96</v>
+        <v>5.01</v>
       </c>
       <c r="O14" t="n">
         <v>0.35</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>14.66</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>45148</v>
+        <v>45149</v>
       </c>
       <c r="H15" t="n">
-        <v>858.1</v>
+        <v>864.55</v>
       </c>
       <c r="I15" t="n">
         <v>860.0300425056992</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K15" t="n">
-        <v>-7</v>
+        <v>-7.8</v>
       </c>
       <c r="L15" t="n">
         <v>10.69</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>11.3</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45224</v>
+        <v>45225</v>
       </c>
       <c r="H16" t="n">
-        <v>916.5</v>
+        <v>875.95</v>
       </c>
       <c r="I16" t="n">
         <v>890.8567542427496</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K16" t="n">
-        <v>6.01</v>
+        <v>1.32</v>
       </c>
       <c r="L16" t="n">
         <v>4.57</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>15.39</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45303</v>
+        <v>45306</v>
       </c>
       <c r="H17" t="n">
-        <v>692.45</v>
+        <v>714.2</v>
       </c>
       <c r="I17" t="n">
         <v>702.1378276339946</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="K17" t="n">
-        <v>20.95</v>
+        <v>18.47</v>
       </c>
       <c r="L17" t="n">
         <v>8.76</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>10.32</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45322</v>
+        <v>45323</v>
       </c>
       <c r="H18" t="n">
-        <v>761.2</v>
+        <v>609</v>
       </c>
       <c r="I18" t="n">
         <v>711.2538273019842</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K18" t="n">
-        <v>6.58</v>
+        <v>-14.73</v>
       </c>
       <c r="L18" t="n">
-        <v>4.31</v>
+        <v>14.73</v>
       </c>
       <c r="M18" t="n">
-        <v>0.72</v>
+        <v>19.99</v>
       </c>
       <c r="N18" t="n">
-        <v>3.74</v>
+        <v>19.99</v>
       </c>
       <c r="O18" t="n">
         <v>3.14</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>18.22</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45433</v>
+        <v>45434</v>
       </c>
       <c r="H19" t="n">
-        <v>351.7</v>
+        <v>368.85</v>
       </c>
       <c r="I19" t="n">
         <v>365.538430490904</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K19" t="n">
-        <v>42.25</v>
+        <v>39.43</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>4</v>
+      </c>
+      <c r="U19" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>15.69</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45664</v>
+        <v>45665</v>
       </c>
       <c r="H20" t="n">
-        <v>983.2</v>
+        <v>902.05</v>
       </c>
       <c r="I20" t="n">
         <v>909.691003274419</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K20" t="n">
-        <v>166.56</v>
+        <v>144.56</v>
       </c>
       <c r="L20" t="n">
         <v>8.08</v>
@@ -1581,7 +1820,7 @@
         <v>3.88</v>
       </c>
       <c r="N20" t="n">
-        <v>6.23</v>
+        <v>8.25</v>
       </c>
       <c r="O20" t="n">
         <v>4.88</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>158</v>
+        <v>159</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>9</v>
+      </c>
+      <c r="U20" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>17.92</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45742</v>
+        <v>45743</v>
       </c>
       <c r="H21" t="n">
-        <v>776.9</v>
+        <v>810.1</v>
       </c>
       <c r="I21" t="n">
         <v>786.0738985928567</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K21" t="n">
-        <v>13.87</v>
+        <v>10.19</v>
       </c>
       <c r="L21" t="n">
         <v>9.449999999999999</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>15.62</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45821</v>
+        <v>45824</v>
       </c>
       <c r="H22" t="n">
-        <v>882.25</v>
+        <v>877.35</v>
       </c>
       <c r="I22" t="n">
         <v>881.526106994729</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="K22" t="n">
-        <v>8.91</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="L22" t="n">
         <v>7.04</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>11.14</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45849</v>
+        <v>45852</v>
       </c>
       <c r="H23" t="n">
-        <v>951.15</v>
+        <v>974.7</v>
       </c>
       <c r="I23" t="n">
         <v>965.0271346778528</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K23" t="n">
-        <v>-8.41</v>
+        <v>-11.1</v>
       </c>
       <c r="L23" t="n">
-        <v>9.119999999999999</v>
+        <v>11.68</v>
       </c>
       <c r="M23" t="n">
         <v>1.28</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>10.16</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="H24" t="n">
-        <v>1179.4</v>
+        <v>1162.2</v>
       </c>
       <c r="I24" t="n">
         <v>1165.533102930944</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K24" t="n">
-        <v>21</v>
+        <v>19.24</v>
       </c>
       <c r="L24" t="n">
         <v>4.06</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>9.300000000000001</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="H25" t="n">
-        <v>1168</v>
+        <v>1224.2</v>
       </c>
       <c r="I25" t="n">
         <v>1210.502500003583</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.5</v>
+        <v>-5.33</v>
       </c>
       <c r="L25" t="n">
-        <v>2</v>
+        <v>5.83</v>
       </c>
       <c r="M25" t="n">
         <v>0.43</v>
       </c>
       <c r="N25" t="n">
-        <v>2.21</v>
+        <v>4.81</v>
       </c>
       <c r="O25" t="n">
         <v>-1.46</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>11.28</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="H26" t="n">
-        <v>1296.8</v>
+        <v>1235.9</v>
       </c>
       <c r="I26" t="n">
         <v>1265.620830126949</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K26" t="n">
-        <v>5.93</v>
+        <v>0.96</v>
       </c>
       <c r="L26" t="n">
         <v>5.24</v>
@@ -1923,7 +2234,7 @@
         <v>1.42</v>
       </c>
       <c r="N26" t="n">
-        <v>3.68</v>
+        <v>4.7</v>
       </c>
       <c r="O26" t="n">
         <v>4.81</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>4</v>
+      </c>
+      <c r="U26" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>11.99</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="H27" t="n">
-        <v>1028.45</v>
+        <v>1112.95</v>
       </c>
       <c r="I27" t="n">
         <v>1102.864361257974</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K27" t="n">
-        <v>16.79</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="L27" t="n">
         <v>5.49</v>
@@ -1980,7 +2303,7 @@
         <v>4.15</v>
       </c>
       <c r="N27" t="n">
-        <v>5.32</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="O27" t="n">
         <v>-4.7</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>4</v>
+      </c>
+      <c r="U27" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>16.1</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="H28" t="n">
-        <v>1095</v>
+        <v>1070.9</v>
       </c>
       <c r="I28" t="n">
         <v>1075.252279280876</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K28" t="n">
-        <v>-1.61</v>
+        <v>-3.78</v>
       </c>
       <c r="L28" t="n">
         <v>5.56</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>11.29</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="H29" t="n">
-        <v>1141.5</v>
+        <v>1203.7</v>
       </c>
       <c r="I29" t="n">
         <v>1154.746213158614</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K29" t="n">
-        <v>-6.59</v>
+        <v>-12.4</v>
       </c>
       <c r="L29" t="n">
-        <v>8.25</v>
+        <v>12.9</v>
       </c>
       <c r="M29" t="n">
         <v>1.29</v>
       </c>
       <c r="N29" t="n">
-        <v>4.97</v>
+        <v>5.45</v>
       </c>
       <c r="O29" t="n">
         <v>-2.2</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>11.43</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="H30" t="n">
-        <v>1661.4</v>
+        <v>1616.1</v>
       </c>
       <c r="I30" t="n">
         <v>1621.571389801226</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K30" t="n">
-        <v>38.02</v>
+        <v>34.26</v>
       </c>
       <c r="L30" t="n">
         <v>4.42</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>4</v>
+      </c>
+      <c r="U30" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -2211,6 +2582,14 @@
       <c r="Q31" t="n">
         <v>4</v>
       </c>
+      <c r="R31" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4381,7 +4760,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>59.8</v>
+        <v>61.6</v>
       </c>
     </row>
     <row r="6">
@@ -4391,7 +4770,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7">
@@ -4401,7 +4780,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="8">
@@ -4411,7 +4790,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -4421,7 +4800,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10">
@@ -4431,7 +4810,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>109.2</v>
+        <v>111.2</v>
       </c>
     </row>
     <row r="11">
@@ -4471,7 +4850,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>11.78</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="15">
@@ -4481,7 +4860,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15.49</v>
+        <v>9.890000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -4491,7 +4870,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7.81</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="17">
@@ -4501,7 +4880,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>166.56</v>
+        <v>144.56</v>
       </c>
     </row>
     <row r="18">
@@ -4511,7 +4890,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>55.2</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="19">
@@ -4521,7 +4900,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>9.050000000000001</v>
+        <v>10.55</v>
       </c>
     </row>
     <row r="20">
@@ -4531,7 +4910,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7.04</v>
+        <v>8.76</v>
       </c>
     </row>
     <row r="21">
@@ -4541,7 +4920,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>30.49</v>
+        <v>35.96</v>
       </c>
     </row>
     <row r="22">
@@ -4551,7 +4930,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23">
@@ -4561,7 +4940,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
@@ -4571,7 +4950,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.83</v>
+        <v>3.68</v>
       </c>
     </row>
     <row r="25">
@@ -4581,7 +4960,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>8.59</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="26">
@@ -4591,7 +4970,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.78</v>
+        <v>7.06</v>
       </c>
     </row>
     <row r="27">
@@ -4601,7 +4980,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="28">
@@ -4611,7 +4990,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29">
